--- a/metodologia_cidades_inteligentes/resultados/Comparacao_Original_vs_RaizPeso.xlsx
+++ b/metodologia_cidades_inteligentes/resultados/Comparacao_Original_vs_RaizPeso.xlsx
@@ -2515,16 +2515,16 @@
         <v>85.49822326767685</v>
       </c>
       <c r="F2">
+        <v>145</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
         <v>181</v>
       </c>
-      <c r="G2">
-        <v>145</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>78</v>
-      </c>
-      <c r="I2">
-        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2544,16 +2544,16 @@
         <v>262.5106728356594</v>
       </c>
       <c r="F3">
+        <v>156</v>
+      </c>
+      <c r="G3">
+        <v>236</v>
+      </c>
+      <c r="H3">
         <v>180</v>
       </c>
-      <c r="G3">
-        <v>156</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>72</v>
-      </c>
-      <c r="I3">
-        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -2591,19 +2591,19 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>181</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2611,19 +2611,19 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>145</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2631,19 +2631,19 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>78</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>199</v>
+        <v>71</v>
       </c>
       <c r="F5">
-        <v>240</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2671,16 +2671,16 @@
         <v>18</v>
       </c>
       <c r="B6">
+        <v>156</v>
+      </c>
+      <c r="C6">
+        <v>236</v>
+      </c>
+      <c r="D6">
         <v>180</v>
       </c>
-      <c r="C6">
-        <v>156</v>
-      </c>
-      <c r="D6">
+      <c r="E6">
         <v>72</v>
-      </c>
-      <c r="E6">
-        <v>236</v>
       </c>
       <c r="F6">
         <v>644</v>
@@ -2748,10 +2748,10 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -2792,10 +2792,10 @@
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -2836,10 +2836,10 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -2880,10 +2880,10 @@
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -2924,10 +2924,10 @@
         <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -2968,10 +2968,10 @@
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -3012,10 +3012,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -3056,10 +3056,10 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -3100,10 +3100,10 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -3144,10 +3144,10 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -3188,10 +3188,10 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -3232,10 +3232,10 @@
         <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -3276,10 +3276,10 @@
         <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -3320,10 +3320,10 @@
         <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -3364,10 +3364,10 @@
         <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -3408,10 +3408,10 @@
         <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -3452,10 +3452,10 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -3496,10 +3496,10 @@
         <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -3540,10 +3540,10 @@
         <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -3584,10 +3584,10 @@
         <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -3628,10 +3628,10 @@
         <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
@@ -3672,10 +3672,10 @@
         <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -3716,10 +3716,10 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
@@ -3760,10 +3760,10 @@
         <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -3848,10 +3848,10 @@
         <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -3892,10 +3892,10 @@
         <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -3936,10 +3936,10 @@
         <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -3980,10 +3980,10 @@
         <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -4024,10 +4024,10 @@
         <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -4068,10 +4068,10 @@
         <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -4112,10 +4112,10 @@
         <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -4156,10 +4156,10 @@
         <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
@@ -4200,10 +4200,10 @@
         <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -4244,10 +4244,10 @@
         <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -4288,10 +4288,10 @@
         <v>69</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -4332,10 +4332,10 @@
         <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
@@ -4376,10 +4376,10 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -4420,10 +4420,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -4464,10 +4464,10 @@
         <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
@@ -4508,10 +4508,10 @@
         <v>74</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
@@ -4552,10 +4552,10 @@
         <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -4596,10 +4596,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -4640,10 +4640,10 @@
         <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -4684,10 +4684,10 @@
         <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -4728,10 +4728,10 @@
         <v>79</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -4772,10 +4772,10 @@
         <v>80</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
@@ -4816,10 +4816,10 @@
         <v>81</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -4860,10 +4860,10 @@
         <v>82</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
@@ -4904,10 +4904,10 @@
         <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -4948,10 +4948,10 @@
         <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -4992,10 +4992,10 @@
         <v>85</v>
       </c>
       <c r="C53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -5036,10 +5036,10 @@
         <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -5080,10 +5080,10 @@
         <v>87</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -5124,10 +5124,10 @@
         <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -5168,10 +5168,10 @@
         <v>89</v>
       </c>
       <c r="C57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -5212,10 +5212,10 @@
         <v>90</v>
       </c>
       <c r="C58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -5256,10 +5256,10 @@
         <v>91</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -5300,10 +5300,10 @@
         <v>92</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
@@ -5344,10 +5344,10 @@
         <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
@@ -5388,10 +5388,10 @@
         <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
@@ -5432,10 +5432,10 @@
         <v>95</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
@@ -5476,10 +5476,10 @@
         <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
@@ -5520,10 +5520,10 @@
         <v>97</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
@@ -5564,10 +5564,10 @@
         <v>98</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
@@ -5608,10 +5608,10 @@
         <v>99</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
@@ -5652,10 +5652,10 @@
         <v>100</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
@@ -5696,10 +5696,10 @@
         <v>101</v>
       </c>
       <c r="C69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
@@ -5740,10 +5740,10 @@
         <v>102</v>
       </c>
       <c r="C70" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
@@ -5784,10 +5784,10 @@
         <v>103</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
@@ -5828,10 +5828,10 @@
         <v>104</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -5872,10 +5872,10 @@
         <v>105</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
@@ -5916,10 +5916,10 @@
         <v>106</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E74" t="b">
         <v>1</v>
@@ -5960,10 +5960,10 @@
         <v>107</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
@@ -6004,10 +6004,10 @@
         <v>108</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
@@ -6048,10 +6048,10 @@
         <v>109</v>
       </c>
       <c r="C77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
@@ -6092,10 +6092,10 @@
         <v>110</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
@@ -6136,10 +6136,10 @@
         <v>111</v>
       </c>
       <c r="C79" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
@@ -6180,10 +6180,10 @@
         <v>112</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>113</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E81" t="b">
         <v>1</v>
@@ -6268,10 +6268,10 @@
         <v>114</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
@@ -6312,10 +6312,10 @@
         <v>115</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
@@ -6356,10 +6356,10 @@
         <v>116</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
@@ -6400,10 +6400,10 @@
         <v>117</v>
       </c>
       <c r="C85" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
@@ -6444,10 +6444,10 @@
         <v>118</v>
       </c>
       <c r="C86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>119</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E87" t="b">
         <v>1</v>
@@ -6532,10 +6532,10 @@
         <v>120</v>
       </c>
       <c r="C88" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
@@ -6576,10 +6576,10 @@
         <v>121</v>
       </c>
       <c r="C89" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
@@ -6620,10 +6620,10 @@
         <v>122</v>
       </c>
       <c r="C90" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
@@ -6664,10 +6664,10 @@
         <v>123</v>
       </c>
       <c r="C91" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E91" t="b">
         <v>1</v>
@@ -6708,10 +6708,10 @@
         <v>124</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
@@ -6752,10 +6752,10 @@
         <v>125</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
@@ -6796,10 +6796,10 @@
         <v>126</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
@@ -6840,10 +6840,10 @@
         <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
@@ -6884,10 +6884,10 @@
         <v>128</v>
       </c>
       <c r="C96" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D96" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
@@ -6928,10 +6928,10 @@
         <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
@@ -6972,10 +6972,10 @@
         <v>130</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E98" t="b">
         <v>1</v>
@@ -7016,10 +7016,10 @@
         <v>131</v>
       </c>
       <c r="C99" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
@@ -7060,10 +7060,10 @@
         <v>132</v>
       </c>
       <c r="C100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
@@ -7104,10 +7104,10 @@
         <v>133</v>
       </c>
       <c r="C101" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
@@ -7148,10 +7148,10 @@
         <v>134</v>
       </c>
       <c r="C102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
@@ -7192,10 +7192,10 @@
         <v>135</v>
       </c>
       <c r="C103" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
@@ -7236,10 +7236,10 @@
         <v>136</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
@@ -7280,10 +7280,10 @@
         <v>137</v>
       </c>
       <c r="C105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
@@ -7324,10 +7324,10 @@
         <v>138</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>139</v>
       </c>
       <c r="C107" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
@@ -7412,10 +7412,10 @@
         <v>140</v>
       </c>
       <c r="C108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
@@ -7456,10 +7456,10 @@
         <v>141</v>
       </c>
       <c r="C109" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
@@ -7500,10 +7500,10 @@
         <v>142</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>143</v>
       </c>
       <c r="C111" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
@@ -7588,10 +7588,10 @@
         <v>144</v>
       </c>
       <c r="C112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
@@ -7632,10 +7632,10 @@
         <v>145</v>
       </c>
       <c r="C113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
@@ -7676,10 +7676,10 @@
         <v>146</v>
       </c>
       <c r="C114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
@@ -7720,10 +7720,10 @@
         <v>147</v>
       </c>
       <c r="C115" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D115" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
@@ -7764,10 +7764,10 @@
         <v>148</v>
       </c>
       <c r="C116" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D116" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
@@ -7808,10 +7808,10 @@
         <v>149</v>
       </c>
       <c r="C117" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D117" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
@@ -7852,10 +7852,10 @@
         <v>150</v>
       </c>
       <c r="C118" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D118" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
@@ -7896,10 +7896,10 @@
         <v>151</v>
       </c>
       <c r="C119" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
@@ -7940,10 +7940,10 @@
         <v>152</v>
       </c>
       <c r="C120" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D120" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
@@ -7984,10 +7984,10 @@
         <v>153</v>
       </c>
       <c r="C121" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E121" t="b">
         <v>1</v>
@@ -8028,10 +8028,10 @@
         <v>154</v>
       </c>
       <c r="C122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>155</v>
       </c>
       <c r="C123" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D123" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E123" t="b">
         <v>1</v>
@@ -8116,10 +8116,10 @@
         <v>156</v>
       </c>
       <c r="C124" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D124" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
@@ -8160,10 +8160,10 @@
         <v>157</v>
       </c>
       <c r="C125" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D125" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
@@ -8204,10 +8204,10 @@
         <v>158</v>
       </c>
       <c r="C126" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E126" t="b">
         <v>1</v>
@@ -8248,10 +8248,10 @@
         <v>159</v>
       </c>
       <c r="C127" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D127" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
@@ -8292,10 +8292,10 @@
         <v>160</v>
       </c>
       <c r="C128" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D128" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E128" t="b">
         <v>1</v>
@@ -8336,10 +8336,10 @@
         <v>161</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D129" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
@@ -8380,10 +8380,10 @@
         <v>162</v>
       </c>
       <c r="C130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
@@ -8424,10 +8424,10 @@
         <v>163</v>
       </c>
       <c r="C131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
@@ -8468,10 +8468,10 @@
         <v>164</v>
       </c>
       <c r="C132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
@@ -8512,10 +8512,10 @@
         <v>165</v>
       </c>
       <c r="C133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
@@ -8556,10 +8556,10 @@
         <v>166</v>
       </c>
       <c r="C134" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D134" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
@@ -8600,10 +8600,10 @@
         <v>167</v>
       </c>
       <c r="C135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
@@ -8644,10 +8644,10 @@
         <v>168</v>
       </c>
       <c r="C136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E136" t="b">
         <v>1</v>
@@ -8688,10 +8688,10 @@
         <v>169</v>
       </c>
       <c r="C137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
@@ -8732,10 +8732,10 @@
         <v>170</v>
       </c>
       <c r="C138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E138" t="b">
         <v>1</v>
@@ -8776,10 +8776,10 @@
         <v>171</v>
       </c>
       <c r="C139" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D139" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
@@ -8820,10 +8820,10 @@
         <v>172</v>
       </c>
       <c r="C140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E140" t="b">
         <v>1</v>
@@ -8864,10 +8864,10 @@
         <v>173</v>
       </c>
       <c r="C141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E141" t="b">
         <v>1</v>
@@ -8908,10 +8908,10 @@
         <v>174</v>
       </c>
       <c r="C142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
@@ -8952,10 +8952,10 @@
         <v>175</v>
       </c>
       <c r="C143" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D143" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
@@ -8996,10 +8996,10 @@
         <v>176</v>
       </c>
       <c r="C144" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D144" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
@@ -9040,10 +9040,10 @@
         <v>177</v>
       </c>
       <c r="C145" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D145" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
@@ -9084,10 +9084,10 @@
         <v>178</v>
       </c>
       <c r="C146" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D146" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
@@ -9128,10 +9128,10 @@
         <v>179</v>
       </c>
       <c r="C147" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D147" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
@@ -9172,10 +9172,10 @@
         <v>180</v>
       </c>
       <c r="C148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
@@ -9216,10 +9216,10 @@
         <v>181</v>
       </c>
       <c r="C149" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E149" t="b">
         <v>1</v>
@@ -9260,10 +9260,10 @@
         <v>182</v>
       </c>
       <c r="C150" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
@@ -9304,10 +9304,10 @@
         <v>183</v>
       </c>
       <c r="C151" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E151" t="b">
         <v>1</v>
@@ -9348,10 +9348,10 @@
         <v>184</v>
       </c>
       <c r="C152" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D152" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
@@ -9392,10 +9392,10 @@
         <v>185</v>
       </c>
       <c r="C153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
@@ -9436,10 +9436,10 @@
         <v>186</v>
       </c>
       <c r="C154" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D154" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>187</v>
       </c>
       <c r="C155" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D155" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
@@ -9524,10 +9524,10 @@
         <v>188</v>
       </c>
       <c r="C156" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D156" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
@@ -9568,10 +9568,10 @@
         <v>189</v>
       </c>
       <c r="C157" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D157" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
@@ -9612,10 +9612,10 @@
         <v>190</v>
       </c>
       <c r="C158" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D158" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
@@ -9656,10 +9656,10 @@
         <v>191</v>
       </c>
       <c r="C159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
@@ -9700,10 +9700,10 @@
         <v>192</v>
       </c>
       <c r="C160" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
@@ -9744,10 +9744,10 @@
         <v>193</v>
       </c>
       <c r="C161" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D161" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E161" t="b">
         <v>1</v>
@@ -9788,10 +9788,10 @@
         <v>194</v>
       </c>
       <c r="C162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
@@ -9832,10 +9832,10 @@
         <v>195</v>
       </c>
       <c r="C163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
@@ -9876,10 +9876,10 @@
         <v>196</v>
       </c>
       <c r="C164" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D164" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
@@ -9920,10 +9920,10 @@
         <v>197</v>
       </c>
       <c r="C165" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
@@ -9964,10 +9964,10 @@
         <v>198</v>
       </c>
       <c r="C166" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D166" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
@@ -10008,10 +10008,10 @@
         <v>199</v>
       </c>
       <c r="C167" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E167" t="b">
         <v>1</v>
@@ -10052,10 +10052,10 @@
         <v>200</v>
       </c>
       <c r="C168" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
@@ -10096,10 +10096,10 @@
         <v>201</v>
       </c>
       <c r="C169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
@@ -10140,10 +10140,10 @@
         <v>202</v>
       </c>
       <c r="C170" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D170" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
@@ -10184,10 +10184,10 @@
         <v>203</v>
       </c>
       <c r="C171" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D171" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E171" t="b">
         <v>1</v>
@@ -10228,10 +10228,10 @@
         <v>204</v>
       </c>
       <c r="C172" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D172" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
@@ -10272,10 +10272,10 @@
         <v>205</v>
       </c>
       <c r="C173" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D173" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
@@ -10316,10 +10316,10 @@
         <v>206</v>
       </c>
       <c r="C174" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D174" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
@@ -10360,10 +10360,10 @@
         <v>207</v>
       </c>
       <c r="C175" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D175" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
@@ -10404,10 +10404,10 @@
         <v>208</v>
       </c>
       <c r="C176" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
@@ -10448,10 +10448,10 @@
         <v>209</v>
       </c>
       <c r="C177" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D177" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
@@ -10492,10 +10492,10 @@
         <v>210</v>
       </c>
       <c r="C178" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D178" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
@@ -10536,10 +10536,10 @@
         <v>211</v>
       </c>
       <c r="C179" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D179" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
@@ -10580,10 +10580,10 @@
         <v>212</v>
       </c>
       <c r="C180" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D180" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
@@ -10624,10 +10624,10 @@
         <v>213</v>
       </c>
       <c r="C181" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D181" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
@@ -10668,10 +10668,10 @@
         <v>214</v>
       </c>
       <c r="C182" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D182" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E182" t="b">
         <v>1</v>
@@ -10712,10 +10712,10 @@
         <v>215</v>
       </c>
       <c r="C183" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D183" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
@@ -10756,10 +10756,10 @@
         <v>216</v>
       </c>
       <c r="C184" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D184" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
@@ -10800,10 +10800,10 @@
         <v>217</v>
       </c>
       <c r="C185" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D185" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
@@ -10844,10 +10844,10 @@
         <v>218</v>
       </c>
       <c r="C186" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D186" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
@@ -10888,10 +10888,10 @@
         <v>219</v>
       </c>
       <c r="C187" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D187" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E187" t="b">
         <v>1</v>
@@ -10932,10 +10932,10 @@
         <v>220</v>
       </c>
       <c r="C188" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D188" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
@@ -10976,10 +10976,10 @@
         <v>221</v>
       </c>
       <c r="C189" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D189" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
@@ -11020,10 +11020,10 @@
         <v>222</v>
       </c>
       <c r="C190" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D190" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
@@ -11064,10 +11064,10 @@
         <v>223</v>
       </c>
       <c r="C191" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D191" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
@@ -11108,10 +11108,10 @@
         <v>224</v>
       </c>
       <c r="C192" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D192" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
@@ -11152,10 +11152,10 @@
         <v>225</v>
       </c>
       <c r="C193" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D193" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
@@ -11196,10 +11196,10 @@
         <v>226</v>
       </c>
       <c r="C194" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D194" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
@@ -11240,10 +11240,10 @@
         <v>227</v>
       </c>
       <c r="C195" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D195" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
@@ -11284,10 +11284,10 @@
         <v>228</v>
       </c>
       <c r="C196" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D196" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
@@ -11328,10 +11328,10 @@
         <v>229</v>
       </c>
       <c r="C197" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D197" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
@@ -11372,10 +11372,10 @@
         <v>230</v>
       </c>
       <c r="C198" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D198" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
@@ -11416,10 +11416,10 @@
         <v>231</v>
       </c>
       <c r="C199" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D199" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E199" t="b">
         <v>1</v>
@@ -11460,10 +11460,10 @@
         <v>232</v>
       </c>
       <c r="C200" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D200" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E200" t="b">
         <v>1</v>
@@ -11504,10 +11504,10 @@
         <v>233</v>
       </c>
       <c r="C201" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D201" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
@@ -11548,10 +11548,10 @@
         <v>234</v>
       </c>
       <c r="C202" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D202" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E202" t="b">
         <v>0</v>
@@ -11592,10 +11592,10 @@
         <v>235</v>
       </c>
       <c r="C203" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D203" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E203" t="b">
         <v>0</v>
@@ -11636,10 +11636,10 @@
         <v>236</v>
       </c>
       <c r="C204" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D204" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E204" t="b">
         <v>0</v>
@@ -11680,10 +11680,10 @@
         <v>237</v>
       </c>
       <c r="C205" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D205" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E205" t="b">
         <v>0</v>
@@ -11724,10 +11724,10 @@
         <v>238</v>
       </c>
       <c r="C206" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D206" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E206" t="b">
         <v>0</v>
@@ -11768,10 +11768,10 @@
         <v>239</v>
       </c>
       <c r="C207" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D207" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E207" t="b">
         <v>1</v>
@@ -11812,10 +11812,10 @@
         <v>240</v>
       </c>
       <c r="C208" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D208" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E208" t="b">
         <v>0</v>
@@ -11856,10 +11856,10 @@
         <v>241</v>
       </c>
       <c r="C209" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D209" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E209" t="b">
         <v>0</v>
@@ -11900,10 +11900,10 @@
         <v>242</v>
       </c>
       <c r="C210" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D210" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E210" t="b">
         <v>0</v>
@@ -11944,10 +11944,10 @@
         <v>243</v>
       </c>
       <c r="C211" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D211" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E211" t="b">
         <v>0</v>
@@ -11988,10 +11988,10 @@
         <v>244</v>
       </c>
       <c r="C212" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D212" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E212" t="b">
         <v>0</v>
@@ -12032,10 +12032,10 @@
         <v>245</v>
       </c>
       <c r="C213" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D213" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E213" t="b">
         <v>0</v>
@@ -12076,10 +12076,10 @@
         <v>246</v>
       </c>
       <c r="C214" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D214" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E214" t="b">
         <v>0</v>
@@ -12120,10 +12120,10 @@
         <v>247</v>
       </c>
       <c r="C215" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D215" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E215" t="b">
         <v>1</v>
@@ -12164,10 +12164,10 @@
         <v>248</v>
       </c>
       <c r="C216" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D216" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E216" t="b">
         <v>0</v>
@@ -12208,10 +12208,10 @@
         <v>249</v>
       </c>
       <c r="C217" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D217" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E217" t="b">
         <v>0</v>
@@ -12252,10 +12252,10 @@
         <v>250</v>
       </c>
       <c r="C218" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D218" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E218" t="b">
         <v>1</v>
@@ -12296,10 +12296,10 @@
         <v>251</v>
       </c>
       <c r="C219" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D219" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E219" t="b">
         <v>1</v>
@@ -12340,10 +12340,10 @@
         <v>252</v>
       </c>
       <c r="C220" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D220" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E220" t="b">
         <v>0</v>
@@ -12384,10 +12384,10 @@
         <v>253</v>
       </c>
       <c r="C221" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D221" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E221" t="b">
         <v>0</v>
@@ -12428,10 +12428,10 @@
         <v>254</v>
       </c>
       <c r="C222" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D222" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E222" t="b">
         <v>0</v>
@@ -12472,10 +12472,10 @@
         <v>255</v>
       </c>
       <c r="C223" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D223" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E223" t="b">
         <v>0</v>
@@ -12516,10 +12516,10 @@
         <v>256</v>
       </c>
       <c r="C224" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D224" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E224" t="b">
         <v>0</v>
@@ -12560,10 +12560,10 @@
         <v>257</v>
       </c>
       <c r="C225" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D225" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E225" t="b">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>258</v>
       </c>
       <c r="C226" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D226" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E226" t="b">
         <v>0</v>
@@ -12648,10 +12648,10 @@
         <v>259</v>
       </c>
       <c r="C227" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D227" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E227" t="b">
         <v>0</v>
@@ -12692,10 +12692,10 @@
         <v>260</v>
       </c>
       <c r="C228" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D228" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E228" t="b">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D229" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E229" t="b">
         <v>1</v>
@@ -12780,10 +12780,10 @@
         <v>262</v>
       </c>
       <c r="C230" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D230" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E230" t="b">
         <v>0</v>
@@ -12824,10 +12824,10 @@
         <v>263</v>
       </c>
       <c r="C231" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D231" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E231" t="b">
         <v>0</v>
@@ -12868,10 +12868,10 @@
         <v>264</v>
       </c>
       <c r="C232" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D232" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E232" t="b">
         <v>0</v>
@@ -12912,10 +12912,10 @@
         <v>265</v>
       </c>
       <c r="C233" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D233" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E233" t="b">
         <v>0</v>
@@ -12956,10 +12956,10 @@
         <v>266</v>
       </c>
       <c r="C234" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D234" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E234" t="b">
         <v>0</v>
@@ -13000,10 +13000,10 @@
         <v>267</v>
       </c>
       <c r="C235" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D235" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E235" t="b">
         <v>0</v>
@@ -13044,10 +13044,10 @@
         <v>268</v>
       </c>
       <c r="C236" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D236" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E236" t="b">
         <v>0</v>
@@ -13088,10 +13088,10 @@
         <v>269</v>
       </c>
       <c r="C237" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D237" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E237" t="b">
         <v>0</v>
@@ -13132,10 +13132,10 @@
         <v>270</v>
       </c>
       <c r="C238" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D238" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E238" t="b">
         <v>0</v>
@@ -13176,10 +13176,10 @@
         <v>271</v>
       </c>
       <c r="C239" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D239" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E239" t="b">
         <v>0</v>
@@ -13220,10 +13220,10 @@
         <v>272</v>
       </c>
       <c r="C240" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D240" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E240" t="b">
         <v>0</v>
@@ -13264,10 +13264,10 @@
         <v>273</v>
       </c>
       <c r="C241" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D241" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E241" t="b">
         <v>0</v>
@@ -13308,10 +13308,10 @@
         <v>274</v>
       </c>
       <c r="C242" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D242" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E242" t="b">
         <v>0</v>
@@ -13352,10 +13352,10 @@
         <v>275</v>
       </c>
       <c r="C243" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D243" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E243" t="b">
         <v>0</v>
@@ -13396,10 +13396,10 @@
         <v>276</v>
       </c>
       <c r="C244" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D244" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E244" t="b">
         <v>0</v>
@@ -13440,10 +13440,10 @@
         <v>277</v>
       </c>
       <c r="C245" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D245" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E245" t="b">
         <v>0</v>
@@ -13484,10 +13484,10 @@
         <v>278</v>
       </c>
       <c r="C246" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D246" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E246" t="b">
         <v>0</v>
@@ -13528,10 +13528,10 @@
         <v>279</v>
       </c>
       <c r="C247" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D247" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E247" t="b">
         <v>0</v>
@@ -13572,10 +13572,10 @@
         <v>280</v>
       </c>
       <c r="C248" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D248" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E248" t="b">
         <v>0</v>
@@ -13616,10 +13616,10 @@
         <v>281</v>
       </c>
       <c r="C249" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D249" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E249" t="b">
         <v>0</v>
@@ -13660,10 +13660,10 @@
         <v>282</v>
       </c>
       <c r="C250" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D250" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E250" t="b">
         <v>0</v>
@@ -13704,10 +13704,10 @@
         <v>283</v>
       </c>
       <c r="C251" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D251" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E251" t="b">
         <v>0</v>
@@ -13748,10 +13748,10 @@
         <v>284</v>
       </c>
       <c r="C252" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D252" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E252" t="b">
         <v>1</v>
@@ -13792,10 +13792,10 @@
         <v>285</v>
       </c>
       <c r="C253" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D253" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E253" t="b">
         <v>1</v>
@@ -13836,10 +13836,10 @@
         <v>286</v>
       </c>
       <c r="C254" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D254" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E254" t="b">
         <v>0</v>
@@ -13880,10 +13880,10 @@
         <v>287</v>
       </c>
       <c r="C255" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D255" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E255" t="b">
         <v>0</v>
@@ -13924,10 +13924,10 @@
         <v>288</v>
       </c>
       <c r="C256" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D256" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E256" t="b">
         <v>0</v>
@@ -13968,10 +13968,10 @@
         <v>289</v>
       </c>
       <c r="C257" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D257" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E257" t="b">
         <v>0</v>
@@ -14012,10 +14012,10 @@
         <v>290</v>
       </c>
       <c r="C258" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D258" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E258" t="b">
         <v>0</v>
@@ -14056,10 +14056,10 @@
         <v>291</v>
       </c>
       <c r="C259" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D259" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E259" t="b">
         <v>0</v>
@@ -14100,10 +14100,10 @@
         <v>292</v>
       </c>
       <c r="C260" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D260" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E260" t="b">
         <v>0</v>
@@ -14144,10 +14144,10 @@
         <v>293</v>
       </c>
       <c r="C261" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D261" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E261" t="b">
         <v>0</v>
@@ -14188,10 +14188,10 @@
         <v>294</v>
       </c>
       <c r="C262" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D262" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E262" t="b">
         <v>0</v>
@@ -14232,10 +14232,10 @@
         <v>295</v>
       </c>
       <c r="C263" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D263" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E263" t="b">
         <v>0</v>
@@ -14276,10 +14276,10 @@
         <v>296</v>
       </c>
       <c r="C264" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D264" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E264" t="b">
         <v>0</v>
@@ -14320,10 +14320,10 @@
         <v>297</v>
       </c>
       <c r="C265" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D265" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E265" t="b">
         <v>0</v>
@@ -14364,10 +14364,10 @@
         <v>298</v>
       </c>
       <c r="C266" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D266" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E266" t="b">
         <v>1</v>
@@ -14408,10 +14408,10 @@
         <v>299</v>
       </c>
       <c r="C267" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D267" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E267" t="b">
         <v>1</v>
@@ -14452,10 +14452,10 @@
         <v>300</v>
       </c>
       <c r="C268" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D268" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E268" t="b">
         <v>1</v>
@@ -14496,10 +14496,10 @@
         <v>301</v>
       </c>
       <c r="C269" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D269" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E269" t="b">
         <v>0</v>
@@ -14540,10 +14540,10 @@
         <v>302</v>
       </c>
       <c r="C270" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D270" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E270" t="b">
         <v>1</v>
@@ -14584,10 +14584,10 @@
         <v>303</v>
       </c>
       <c r="C271" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D271" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E271" t="b">
         <v>0</v>
@@ -14628,10 +14628,10 @@
         <v>304</v>
       </c>
       <c r="C272" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D272" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E272" t="b">
         <v>0</v>
@@ -14672,10 +14672,10 @@
         <v>305</v>
       </c>
       <c r="C273" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D273" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E273" t="b">
         <v>0</v>
@@ -14716,10 +14716,10 @@
         <v>306</v>
       </c>
       <c r="C274" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D274" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E274" t="b">
         <v>0</v>
@@ -14760,10 +14760,10 @@
         <v>307</v>
       </c>
       <c r="C275" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D275" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E275" t="b">
         <v>0</v>
@@ -14804,10 +14804,10 @@
         <v>308</v>
       </c>
       <c r="C276" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D276" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E276" t="b">
         <v>0</v>
@@ -14848,10 +14848,10 @@
         <v>309</v>
       </c>
       <c r="C277" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D277" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E277" t="b">
         <v>1</v>
@@ -14892,10 +14892,10 @@
         <v>310</v>
       </c>
       <c r="C278" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D278" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E278" t="b">
         <v>0</v>
@@ -14936,10 +14936,10 @@
         <v>311</v>
       </c>
       <c r="C279" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D279" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E279" t="b">
         <v>1</v>
@@ -14980,10 +14980,10 @@
         <v>312</v>
       </c>
       <c r="C280" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D280" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E280" t="b">
         <v>0</v>
@@ -15024,10 +15024,10 @@
         <v>313</v>
       </c>
       <c r="C281" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D281" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E281" t="b">
         <v>0</v>
@@ -15068,10 +15068,10 @@
         <v>314</v>
       </c>
       <c r="C282" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D282" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E282" t="b">
         <v>0</v>
@@ -15112,10 +15112,10 @@
         <v>315</v>
       </c>
       <c r="C283" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D283" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E283" t="b">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>316</v>
       </c>
       <c r="C284" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D284" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E284" t="b">
         <v>0</v>
@@ -15200,10 +15200,10 @@
         <v>317</v>
       </c>
       <c r="C285" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D285" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E285" t="b">
         <v>1</v>
@@ -15244,10 +15244,10 @@
         <v>318</v>
       </c>
       <c r="C286" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D286" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E286" t="b">
         <v>0</v>
@@ -15288,10 +15288,10 @@
         <v>319</v>
       </c>
       <c r="C287" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D287" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E287" t="b">
         <v>0</v>
@@ -15332,10 +15332,10 @@
         <v>320</v>
       </c>
       <c r="C288" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D288" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E288" t="b">
         <v>0</v>
@@ -15376,10 +15376,10 @@
         <v>321</v>
       </c>
       <c r="C289" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D289" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E289" t="b">
         <v>0</v>
@@ -15420,10 +15420,10 @@
         <v>322</v>
       </c>
       <c r="C290" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D290" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E290" t="b">
         <v>0</v>
@@ -15464,10 +15464,10 @@
         <v>323</v>
       </c>
       <c r="C291" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D291" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E291" t="b">
         <v>0</v>
@@ -15508,10 +15508,10 @@
         <v>324</v>
       </c>
       <c r="C292" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D292" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E292" t="b">
         <v>0</v>
@@ -15552,10 +15552,10 @@
         <v>325</v>
       </c>
       <c r="C293" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D293" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E293" t="b">
         <v>0</v>
@@ -15596,10 +15596,10 @@
         <v>326</v>
       </c>
       <c r="C294" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D294" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E294" t="b">
         <v>0</v>
@@ -15640,10 +15640,10 @@
         <v>327</v>
       </c>
       <c r="C295" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D295" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E295" t="b">
         <v>0</v>
@@ -15684,10 +15684,10 @@
         <v>328</v>
       </c>
       <c r="C296" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D296" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E296" t="b">
         <v>0</v>
@@ -15728,10 +15728,10 @@
         <v>329</v>
       </c>
       <c r="C297" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D297" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E297" t="b">
         <v>0</v>
@@ -15772,10 +15772,10 @@
         <v>330</v>
       </c>
       <c r="C298" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D298" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E298" t="b">
         <v>0</v>
@@ -15816,10 +15816,10 @@
         <v>331</v>
       </c>
       <c r="C299" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D299" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E299" t="b">
         <v>0</v>
@@ -15860,10 +15860,10 @@
         <v>332</v>
       </c>
       <c r="C300" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D300" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E300" t="b">
         <v>0</v>
@@ -15904,10 +15904,10 @@
         <v>333</v>
       </c>
       <c r="C301" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D301" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E301" t="b">
         <v>0</v>
@@ -15948,10 +15948,10 @@
         <v>334</v>
       </c>
       <c r="C302" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D302" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E302" t="b">
         <v>0</v>
@@ -15992,10 +15992,10 @@
         <v>335</v>
       </c>
       <c r="C303" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D303" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E303" t="b">
         <v>0</v>
@@ -16036,10 +16036,10 @@
         <v>336</v>
       </c>
       <c r="C304" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D304" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E304" t="b">
         <v>1</v>
@@ -16080,10 +16080,10 @@
         <v>337</v>
       </c>
       <c r="C305" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D305" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E305" t="b">
         <v>0</v>
@@ -16124,10 +16124,10 @@
         <v>338</v>
       </c>
       <c r="C306" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D306" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E306" t="b">
         <v>0</v>
@@ -16168,10 +16168,10 @@
         <v>339</v>
       </c>
       <c r="C307" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D307" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E307" t="b">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>340</v>
       </c>
       <c r="C308" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D308" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E308" t="b">
         <v>0</v>
@@ -16256,10 +16256,10 @@
         <v>341</v>
       </c>
       <c r="C309" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D309" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E309" t="b">
         <v>0</v>
@@ -16300,10 +16300,10 @@
         <v>342</v>
       </c>
       <c r="C310" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D310" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E310" t="b">
         <v>0</v>
@@ -16344,10 +16344,10 @@
         <v>343</v>
       </c>
       <c r="C311" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D311" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E311" t="b">
         <v>0</v>
@@ -16388,10 +16388,10 @@
         <v>344</v>
       </c>
       <c r="C312" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D312" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E312" t="b">
         <v>0</v>
@@ -16432,10 +16432,10 @@
         <v>345</v>
       </c>
       <c r="C313" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D313" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E313" t="b">
         <v>0</v>
@@ -16476,10 +16476,10 @@
         <v>346</v>
       </c>
       <c r="C314" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D314" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E314" t="b">
         <v>1</v>
@@ -16520,10 +16520,10 @@
         <v>347</v>
       </c>
       <c r="C315" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D315" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E315" t="b">
         <v>1</v>
@@ -16564,10 +16564,10 @@
         <v>348</v>
       </c>
       <c r="C316" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D316" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E316" t="b">
         <v>0</v>
@@ -16608,10 +16608,10 @@
         <v>349</v>
       </c>
       <c r="C317" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D317" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E317" t="b">
         <v>0</v>
@@ -16652,10 +16652,10 @@
         <v>350</v>
       </c>
       <c r="C318" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D318" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E318" t="b">
         <v>0</v>
@@ -16696,10 +16696,10 @@
         <v>351</v>
       </c>
       <c r="C319" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D319" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E319" t="b">
         <v>0</v>
@@ -16740,10 +16740,10 @@
         <v>352</v>
       </c>
       <c r="C320" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D320" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E320" t="b">
         <v>0</v>
@@ -16784,10 +16784,10 @@
         <v>353</v>
       </c>
       <c r="C321" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D321" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E321" t="b">
         <v>0</v>
@@ -16828,10 +16828,10 @@
         <v>354</v>
       </c>
       <c r="C322" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D322" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E322" t="b">
         <v>0</v>
@@ -16872,10 +16872,10 @@
         <v>355</v>
       </c>
       <c r="C323" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D323" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E323" t="b">
         <v>1</v>
@@ -16916,10 +16916,10 @@
         <v>356</v>
       </c>
       <c r="C324" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D324" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E324" t="b">
         <v>0</v>
@@ -16960,10 +16960,10 @@
         <v>357</v>
       </c>
       <c r="C325" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D325" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E325" t="b">
         <v>0</v>
@@ -17004,10 +17004,10 @@
         <v>358</v>
       </c>
       <c r="C326" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D326" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E326" t="b">
         <v>0</v>
@@ -17048,10 +17048,10 @@
         <v>359</v>
       </c>
       <c r="C327" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D327" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E327" t="b">
         <v>0</v>
@@ -17092,10 +17092,10 @@
         <v>360</v>
       </c>
       <c r="C328" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D328" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E328" t="b">
         <v>0</v>
@@ -17136,10 +17136,10 @@
         <v>361</v>
       </c>
       <c r="C329" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D329" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E329" t="b">
         <v>0</v>
@@ -17180,10 +17180,10 @@
         <v>362</v>
       </c>
       <c r="C330" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D330" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E330" t="b">
         <v>0</v>
@@ -17224,10 +17224,10 @@
         <v>363</v>
       </c>
       <c r="C331" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D331" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E331" t="b">
         <v>0</v>
@@ -17268,10 +17268,10 @@
         <v>364</v>
       </c>
       <c r="C332" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D332" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E332" t="b">
         <v>0</v>
@@ -17312,10 +17312,10 @@
         <v>365</v>
       </c>
       <c r="C333" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D333" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E333" t="b">
         <v>0</v>
@@ -17356,10 +17356,10 @@
         <v>366</v>
       </c>
       <c r="C334" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D334" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E334" t="b">
         <v>1</v>
@@ -17400,10 +17400,10 @@
         <v>367</v>
       </c>
       <c r="C335" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D335" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E335" t="b">
         <v>0</v>
@@ -17444,10 +17444,10 @@
         <v>368</v>
       </c>
       <c r="C336" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D336" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E336" t="b">
         <v>0</v>
@@ -17488,10 +17488,10 @@
         <v>369</v>
       </c>
       <c r="C337" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D337" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E337" t="b">
         <v>0</v>
@@ -17532,10 +17532,10 @@
         <v>370</v>
       </c>
       <c r="C338" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D338" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E338" t="b">
         <v>1</v>
@@ -17576,10 +17576,10 @@
         <v>371</v>
       </c>
       <c r="C339" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D339" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E339" t="b">
         <v>1</v>
@@ -17620,10 +17620,10 @@
         <v>372</v>
       </c>
       <c r="C340" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D340" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E340" t="b">
         <v>0</v>
@@ -17664,10 +17664,10 @@
         <v>373</v>
       </c>
       <c r="C341" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D341" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E341" t="b">
         <v>0</v>
@@ -17708,10 +17708,10 @@
         <v>374</v>
       </c>
       <c r="C342" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D342" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E342" t="b">
         <v>0</v>
@@ -17752,10 +17752,10 @@
         <v>375</v>
       </c>
       <c r="C343" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D343" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E343" t="b">
         <v>0</v>
@@ -17796,10 +17796,10 @@
         <v>376</v>
       </c>
       <c r="C344" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D344" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E344" t="b">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>377</v>
       </c>
       <c r="C345" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D345" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E345" t="b">
         <v>0</v>
@@ -17884,10 +17884,10 @@
         <v>378</v>
       </c>
       <c r="C346" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D346" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E346" t="b">
         <v>0</v>
@@ -17928,10 +17928,10 @@
         <v>379</v>
       </c>
       <c r="C347" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D347" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E347" t="b">
         <v>0</v>
@@ -17972,10 +17972,10 @@
         <v>380</v>
       </c>
       <c r="C348" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D348" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E348" t="b">
         <v>0</v>
@@ -18016,10 +18016,10 @@
         <v>381</v>
       </c>
       <c r="C349" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D349" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E349" t="b">
         <v>1</v>
@@ -18060,10 +18060,10 @@
         <v>382</v>
       </c>
       <c r="C350" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D350" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E350" t="b">
         <v>0</v>
@@ -18104,10 +18104,10 @@
         <v>383</v>
       </c>
       <c r="C351" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D351" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E351" t="b">
         <v>1</v>
@@ -18148,10 +18148,10 @@
         <v>384</v>
       </c>
       <c r="C352" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D352" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E352" t="b">
         <v>0</v>
@@ -18192,10 +18192,10 @@
         <v>385</v>
       </c>
       <c r="C353" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D353" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E353" t="b">
         <v>0</v>
@@ -18236,10 +18236,10 @@
         <v>386</v>
       </c>
       <c r="C354" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D354" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E354" t="b">
         <v>0</v>
@@ -18280,10 +18280,10 @@
         <v>387</v>
       </c>
       <c r="C355" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D355" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E355" t="b">
         <v>0</v>
@@ -18324,10 +18324,10 @@
         <v>388</v>
       </c>
       <c r="C356" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D356" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E356" t="b">
         <v>0</v>
@@ -18368,10 +18368,10 @@
         <v>389</v>
       </c>
       <c r="C357" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D357" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E357" t="b">
         <v>0</v>
@@ -18412,10 +18412,10 @@
         <v>390</v>
       </c>
       <c r="C358" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D358" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E358" t="b">
         <v>0</v>
@@ -18456,10 +18456,10 @@
         <v>391</v>
       </c>
       <c r="C359" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D359" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E359" t="b">
         <v>0</v>
@@ -18500,10 +18500,10 @@
         <v>392</v>
       </c>
       <c r="C360" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D360" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E360" t="b">
         <v>0</v>
@@ -18544,10 +18544,10 @@
         <v>393</v>
       </c>
       <c r="C361" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D361" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E361" t="b">
         <v>0</v>
@@ -18588,10 +18588,10 @@
         <v>394</v>
       </c>
       <c r="C362" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D362" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E362" t="b">
         <v>0</v>
@@ -18632,10 +18632,10 @@
         <v>395</v>
       </c>
       <c r="C363" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D363" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E363" t="b">
         <v>0</v>
@@ -18676,10 +18676,10 @@
         <v>396</v>
       </c>
       <c r="C364" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D364" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E364" t="b">
         <v>0</v>
@@ -18720,10 +18720,10 @@
         <v>397</v>
       </c>
       <c r="C365" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D365" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E365" t="b">
         <v>0</v>
@@ -18764,10 +18764,10 @@
         <v>398</v>
       </c>
       <c r="C366" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D366" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E366" t="b">
         <v>1</v>
@@ -18808,10 +18808,10 @@
         <v>399</v>
       </c>
       <c r="C367" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D367" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E367" t="b">
         <v>0</v>
@@ -18852,10 +18852,10 @@
         <v>400</v>
       </c>
       <c r="C368" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D368" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E368" t="b">
         <v>0</v>
@@ -18896,10 +18896,10 @@
         <v>401</v>
       </c>
       <c r="C369" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D369" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E369" t="b">
         <v>1</v>
@@ -18940,10 +18940,10 @@
         <v>402</v>
       </c>
       <c r="C370" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D370" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E370" t="b">
         <v>0</v>
@@ -18984,10 +18984,10 @@
         <v>403</v>
       </c>
       <c r="C371" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D371" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E371" t="b">
         <v>1</v>
@@ -19028,10 +19028,10 @@
         <v>404</v>
       </c>
       <c r="C372" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D372" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E372" t="b">
         <v>0</v>
@@ -19072,10 +19072,10 @@
         <v>405</v>
       </c>
       <c r="C373" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D373" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E373" t="b">
         <v>0</v>
@@ -19116,10 +19116,10 @@
         <v>406</v>
       </c>
       <c r="C374" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D374" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E374" t="b">
         <v>0</v>
@@ -19160,10 +19160,10 @@
         <v>407</v>
       </c>
       <c r="C375" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D375" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E375" t="b">
         <v>0</v>
@@ -19204,10 +19204,10 @@
         <v>408</v>
       </c>
       <c r="C376" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D376" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E376" t="b">
         <v>0</v>
@@ -19248,10 +19248,10 @@
         <v>409</v>
       </c>
       <c r="C377" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D377" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E377" t="b">
         <v>0</v>
@@ -19292,10 +19292,10 @@
         <v>410</v>
       </c>
       <c r="C378" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D378" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E378" t="b">
         <v>0</v>
@@ -19336,10 +19336,10 @@
         <v>411</v>
       </c>
       <c r="C379" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D379" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E379" t="b">
         <v>0</v>
@@ -19380,10 +19380,10 @@
         <v>412</v>
       </c>
       <c r="C380" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D380" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E380" t="b">
         <v>0</v>
@@ -19424,10 +19424,10 @@
         <v>413</v>
       </c>
       <c r="C381" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D381" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E381" t="b">
         <v>0</v>
@@ -19468,10 +19468,10 @@
         <v>414</v>
       </c>
       <c r="C382" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D382" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E382" t="b">
         <v>0</v>
@@ -19512,10 +19512,10 @@
         <v>415</v>
       </c>
       <c r="C383" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D383" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E383" t="b">
         <v>0</v>
@@ -19556,10 +19556,10 @@
         <v>416</v>
       </c>
       <c r="C384" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D384" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E384" t="b">
         <v>0</v>
@@ -19600,10 +19600,10 @@
         <v>417</v>
       </c>
       <c r="C385" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D385" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E385" t="b">
         <v>1</v>
@@ -19644,10 +19644,10 @@
         <v>418</v>
       </c>
       <c r="C386" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D386" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E386" t="b">
         <v>0</v>
@@ -19688,10 +19688,10 @@
         <v>419</v>
       </c>
       <c r="C387" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D387" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E387" t="b">
         <v>0</v>
@@ -19732,10 +19732,10 @@
         <v>420</v>
       </c>
       <c r="C388" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D388" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E388" t="b">
         <v>0</v>
@@ -19776,10 +19776,10 @@
         <v>421</v>
       </c>
       <c r="C389" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D389" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E389" t="b">
         <v>0</v>
@@ -19820,10 +19820,10 @@
         <v>422</v>
       </c>
       <c r="C390" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D390" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E390" t="b">
         <v>0</v>
@@ -19864,10 +19864,10 @@
         <v>423</v>
       </c>
       <c r="C391" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D391" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E391" t="b">
         <v>0</v>
@@ -19908,10 +19908,10 @@
         <v>424</v>
       </c>
       <c r="C392" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D392" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E392" t="b">
         <v>0</v>
@@ -19952,10 +19952,10 @@
         <v>425</v>
       </c>
       <c r="C393" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D393" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E393" t="b">
         <v>0</v>
@@ -19996,10 +19996,10 @@
         <v>426</v>
       </c>
       <c r="C394" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D394" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E394" t="b">
         <v>0</v>
@@ -20040,10 +20040,10 @@
         <v>427</v>
       </c>
       <c r="C395" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D395" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E395" t="b">
         <v>0</v>
@@ -20084,10 +20084,10 @@
         <v>428</v>
       </c>
       <c r="C396" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D396" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E396" t="b">
         <v>0</v>
@@ -20128,10 +20128,10 @@
         <v>429</v>
       </c>
       <c r="C397" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D397" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E397" t="b">
         <v>0</v>
@@ -20172,10 +20172,10 @@
         <v>430</v>
       </c>
       <c r="C398" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D398" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E398" t="b">
         <v>0</v>
@@ -20216,10 +20216,10 @@
         <v>431</v>
       </c>
       <c r="C399" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D399" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E399" t="b">
         <v>1</v>
@@ -20260,10 +20260,10 @@
         <v>432</v>
       </c>
       <c r="C400" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D400" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E400" t="b">
         <v>0</v>
@@ -20304,10 +20304,10 @@
         <v>433</v>
       </c>
       <c r="C401" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D401" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E401" t="b">
         <v>0</v>
@@ -20348,10 +20348,10 @@
         <v>434</v>
       </c>
       <c r="C402" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D402" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E402" t="b">
         <v>0</v>
@@ -20392,10 +20392,10 @@
         <v>435</v>
       </c>
       <c r="C403" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D403" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E403" t="b">
         <v>0</v>
@@ -20436,10 +20436,10 @@
         <v>436</v>
       </c>
       <c r="C404" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D404" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E404" t="b">
         <v>0</v>
@@ -20480,10 +20480,10 @@
         <v>437</v>
       </c>
       <c r="C405" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D405" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E405" t="b">
         <v>0</v>
@@ -20524,10 +20524,10 @@
         <v>438</v>
       </c>
       <c r="C406" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D406" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E406" t="b">
         <v>1</v>
@@ -20568,10 +20568,10 @@
         <v>439</v>
       </c>
       <c r="C407" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D407" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E407" t="b">
         <v>0</v>
@@ -20612,10 +20612,10 @@
         <v>440</v>
       </c>
       <c r="C408" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D408" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E408" t="b">
         <v>0</v>
@@ -20656,10 +20656,10 @@
         <v>441</v>
       </c>
       <c r="C409" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D409" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E409" t="b">
         <v>0</v>
@@ -20700,10 +20700,10 @@
         <v>442</v>
       </c>
       <c r="C410" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D410" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E410" t="b">
         <v>1</v>
@@ -20744,10 +20744,10 @@
         <v>443</v>
       </c>
       <c r="C411" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D411" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E411" t="b">
         <v>1</v>
@@ -20788,10 +20788,10 @@
         <v>444</v>
       </c>
       <c r="C412" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D412" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E412" t="b">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>445</v>
       </c>
       <c r="C413" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D413" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E413" t="b">
         <v>1</v>
@@ -20876,10 +20876,10 @@
         <v>446</v>
       </c>
       <c r="C414" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D414" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E414" t="b">
         <v>0</v>
@@ -20920,10 +20920,10 @@
         <v>447</v>
       </c>
       <c r="C415" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D415" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E415" t="b">
         <v>0</v>
@@ -20964,10 +20964,10 @@
         <v>448</v>
       </c>
       <c r="C416" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D416" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E416" t="b">
         <v>0</v>
@@ -21008,10 +21008,10 @@
         <v>449</v>
       </c>
       <c r="C417" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D417" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E417" t="b">
         <v>0</v>
@@ -21052,10 +21052,10 @@
         <v>450</v>
       </c>
       <c r="C418" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D418" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E418" t="b">
         <v>0</v>
@@ -21096,10 +21096,10 @@
         <v>451</v>
       </c>
       <c r="C419" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D419" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E419" t="b">
         <v>0</v>
@@ -21140,10 +21140,10 @@
         <v>452</v>
       </c>
       <c r="C420" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D420" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E420" t="b">
         <v>0</v>
@@ -21184,10 +21184,10 @@
         <v>453</v>
       </c>
       <c r="C421" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D421" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E421" t="b">
         <v>0</v>
@@ -21228,10 +21228,10 @@
         <v>454</v>
       </c>
       <c r="C422" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D422" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E422" t="b">
         <v>0</v>
@@ -21272,10 +21272,10 @@
         <v>455</v>
       </c>
       <c r="C423" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D423" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E423" t="b">
         <v>0</v>
@@ -21316,10 +21316,10 @@
         <v>456</v>
       </c>
       <c r="C424" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D424" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E424" t="b">
         <v>0</v>
@@ -21360,10 +21360,10 @@
         <v>457</v>
       </c>
       <c r="C425" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D425" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E425" t="b">
         <v>0</v>
@@ -21404,10 +21404,10 @@
         <v>458</v>
       </c>
       <c r="C426" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D426" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E426" t="b">
         <v>0</v>
@@ -21448,10 +21448,10 @@
         <v>459</v>
       </c>
       <c r="C427" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D427" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E427" t="b">
         <v>0</v>
@@ -21492,10 +21492,10 @@
         <v>460</v>
       </c>
       <c r="C428" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D428" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E428" t="b">
         <v>0</v>
@@ -21536,10 +21536,10 @@
         <v>461</v>
       </c>
       <c r="C429" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D429" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E429" t="b">
         <v>1</v>
@@ -21580,10 +21580,10 @@
         <v>462</v>
       </c>
       <c r="C430" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D430" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E430" t="b">
         <v>0</v>
@@ -21624,10 +21624,10 @@
         <v>463</v>
       </c>
       <c r="C431" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D431" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E431" t="b">
         <v>0</v>
@@ -21668,10 +21668,10 @@
         <v>464</v>
       </c>
       <c r="C432" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D432" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E432" t="b">
         <v>0</v>
@@ -21712,10 +21712,10 @@
         <v>465</v>
       </c>
       <c r="C433" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D433" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E433" t="b">
         <v>0</v>
@@ -21756,10 +21756,10 @@
         <v>466</v>
       </c>
       <c r="C434" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D434" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E434" t="b">
         <v>1</v>
@@ -21800,10 +21800,10 @@
         <v>467</v>
       </c>
       <c r="C435" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D435" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E435" t="b">
         <v>0</v>
@@ -21844,10 +21844,10 @@
         <v>468</v>
       </c>
       <c r="C436" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D436" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E436" t="b">
         <v>0</v>
@@ -21888,10 +21888,10 @@
         <v>469</v>
       </c>
       <c r="C437" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D437" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E437" t="b">
         <v>0</v>
@@ -21932,10 +21932,10 @@
         <v>470</v>
       </c>
       <c r="C438" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D438" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E438" t="b">
         <v>0</v>
@@ -21976,10 +21976,10 @@
         <v>471</v>
       </c>
       <c r="C439" t="s">
+        <v>15</v>
+      </c>
+      <c r="D439" t="s">
         <v>17</v>
-      </c>
-      <c r="D439" t="s">
-        <v>16</v>
       </c>
       <c r="E439" t="b">
         <v>1</v>
@@ -22020,10 +22020,10 @@
         <v>472</v>
       </c>
       <c r="C440" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D440" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E440" t="b">
         <v>0</v>
@@ -22064,10 +22064,10 @@
         <v>473</v>
       </c>
       <c r="C441" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D441" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E441" t="b">
         <v>0</v>
@@ -22108,10 +22108,10 @@
         <v>474</v>
       </c>
       <c r="C442" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D442" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E442" t="b">
         <v>0</v>
@@ -22152,10 +22152,10 @@
         <v>475</v>
       </c>
       <c r="C443" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D443" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E443" t="b">
         <v>0</v>
@@ -22196,10 +22196,10 @@
         <v>476</v>
       </c>
       <c r="C444" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D444" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E444" t="b">
         <v>0</v>
@@ -22240,10 +22240,10 @@
         <v>477</v>
       </c>
       <c r="C445" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D445" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E445" t="b">
         <v>0</v>
@@ -22284,10 +22284,10 @@
         <v>478</v>
       </c>
       <c r="C446" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D446" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E446" t="b">
         <v>0</v>
@@ -22328,10 +22328,10 @@
         <v>479</v>
       </c>
       <c r="C447" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D447" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E447" t="b">
         <v>0</v>
@@ -22372,10 +22372,10 @@
         <v>480</v>
       </c>
       <c r="C448" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D448" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E448" t="b">
         <v>0</v>
@@ -22416,10 +22416,10 @@
         <v>481</v>
       </c>
       <c r="C449" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D449" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E449" t="b">
         <v>0</v>
@@ -22460,10 +22460,10 @@
         <v>482</v>
       </c>
       <c r="C450" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D450" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E450" t="b">
         <v>0</v>
@@ -22504,10 +22504,10 @@
         <v>483</v>
       </c>
       <c r="C451" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D451" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E451" t="b">
         <v>0</v>
@@ -22548,10 +22548,10 @@
         <v>484</v>
       </c>
       <c r="C452" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D452" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E452" t="b">
         <v>0</v>
@@ -22592,10 +22592,10 @@
         <v>485</v>
       </c>
       <c r="C453" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D453" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E453" t="b">
         <v>0</v>
@@ -22636,10 +22636,10 @@
         <v>486</v>
       </c>
       <c r="C454" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D454" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E454" t="b">
         <v>0</v>
@@ -22680,10 +22680,10 @@
         <v>487</v>
       </c>
       <c r="C455" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D455" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E455" t="b">
         <v>0</v>
@@ -22724,10 +22724,10 @@
         <v>488</v>
       </c>
       <c r="C456" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D456" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E456" t="b">
         <v>0</v>
@@ -22768,10 +22768,10 @@
         <v>489</v>
       </c>
       <c r="C457" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D457" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E457" t="b">
         <v>0</v>
@@ -22812,10 +22812,10 @@
         <v>490</v>
       </c>
       <c r="C458" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D458" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E458" t="b">
         <v>0</v>
@@ -22856,10 +22856,10 @@
         <v>491</v>
       </c>
       <c r="C459" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D459" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E459" t="b">
         <v>0</v>
@@ -22900,10 +22900,10 @@
         <v>492</v>
       </c>
       <c r="C460" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D460" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E460" t="b">
         <v>0</v>
@@ -22944,10 +22944,10 @@
         <v>493</v>
       </c>
       <c r="C461" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D461" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E461" t="b">
         <v>0</v>
@@ -22988,10 +22988,10 @@
         <v>494</v>
       </c>
       <c r="C462" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D462" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E462" t="b">
         <v>1</v>
@@ -23032,10 +23032,10 @@
         <v>495</v>
       </c>
       <c r="C463" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D463" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E463" t="b">
         <v>0</v>
@@ -23076,10 +23076,10 @@
         <v>496</v>
       </c>
       <c r="C464" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D464" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E464" t="b">
         <v>0</v>
@@ -23120,10 +23120,10 @@
         <v>497</v>
       </c>
       <c r="C465" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D465" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E465" t="b">
         <v>0</v>
@@ -23164,10 +23164,10 @@
         <v>498</v>
       </c>
       <c r="C466" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D466" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E466" t="b">
         <v>0</v>
@@ -23208,10 +23208,10 @@
         <v>499</v>
       </c>
       <c r="C467" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D467" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E467" t="b">
         <v>1</v>
@@ -23252,10 +23252,10 @@
         <v>500</v>
       </c>
       <c r="C468" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D468" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E468" t="b">
         <v>0</v>
@@ -23296,10 +23296,10 @@
         <v>501</v>
       </c>
       <c r="C469" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D469" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E469" t="b">
         <v>0</v>
@@ -23340,10 +23340,10 @@
         <v>502</v>
       </c>
       <c r="C470" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D470" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E470" t="b">
         <v>0</v>
@@ -23384,10 +23384,10 @@
         <v>503</v>
       </c>
       <c r="C471" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D471" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E471" t="b">
         <v>0</v>
@@ -23428,10 +23428,10 @@
         <v>504</v>
       </c>
       <c r="C472" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D472" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E472" t="b">
         <v>0</v>
@@ -23472,10 +23472,10 @@
         <v>505</v>
       </c>
       <c r="C473" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D473" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E473" t="b">
         <v>0</v>
@@ -23516,10 +23516,10 @@
         <v>506</v>
       </c>
       <c r="C474" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D474" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E474" t="b">
         <v>0</v>
@@ -23560,10 +23560,10 @@
         <v>507</v>
       </c>
       <c r="C475" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D475" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E475" t="b">
         <v>0</v>
@@ -23604,10 +23604,10 @@
         <v>508</v>
       </c>
       <c r="C476" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D476" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E476" t="b">
         <v>0</v>
@@ -23648,10 +23648,10 @@
         <v>509</v>
       </c>
       <c r="C477" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D477" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E477" t="b">
         <v>0</v>
@@ -23692,10 +23692,10 @@
         <v>510</v>
       </c>
       <c r="C478" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D478" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E478" t="b">
         <v>1</v>
@@ -23736,10 +23736,10 @@
         <v>511</v>
       </c>
       <c r="C479" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D479" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E479" t="b">
         <v>0</v>
@@ -23780,10 +23780,10 @@
         <v>512</v>
       </c>
       <c r="C480" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D480" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E480" t="b">
         <v>0</v>
@@ -23824,10 +23824,10 @@
         <v>513</v>
       </c>
       <c r="C481" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D481" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E481" t="b">
         <v>0</v>
@@ -23868,10 +23868,10 @@
         <v>514</v>
       </c>
       <c r="C482" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D482" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E482" t="b">
         <v>0</v>
@@ -23912,10 +23912,10 @@
         <v>515</v>
       </c>
       <c r="C483" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D483" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E483" t="b">
         <v>0</v>
@@ -23956,10 +23956,10 @@
         <v>516</v>
       </c>
       <c r="C484" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D484" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E484" t="b">
         <v>0</v>
@@ -24000,10 +24000,10 @@
         <v>517</v>
       </c>
       <c r="C485" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D485" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E485" t="b">
         <v>0</v>
@@ -24044,10 +24044,10 @@
         <v>518</v>
       </c>
       <c r="C486" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D486" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E486" t="b">
         <v>0</v>
@@ -24088,10 +24088,10 @@
         <v>519</v>
       </c>
       <c r="C487" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D487" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E487" t="b">
         <v>0</v>
@@ -24132,10 +24132,10 @@
         <v>520</v>
       </c>
       <c r="C488" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D488" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E488" t="b">
         <v>0</v>
@@ -24176,10 +24176,10 @@
         <v>521</v>
       </c>
       <c r="C489" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D489" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E489" t="b">
         <v>0</v>
@@ -24220,10 +24220,10 @@
         <v>522</v>
       </c>
       <c r="C490" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D490" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E490" t="b">
         <v>0</v>
@@ -24264,10 +24264,10 @@
         <v>523</v>
       </c>
       <c r="C491" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D491" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E491" t="b">
         <v>0</v>
@@ -24308,10 +24308,10 @@
         <v>524</v>
       </c>
       <c r="C492" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D492" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E492" t="b">
         <v>0</v>
@@ -24352,10 +24352,10 @@
         <v>525</v>
       </c>
       <c r="C493" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D493" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E493" t="b">
         <v>0</v>
@@ -24396,10 +24396,10 @@
         <v>526</v>
       </c>
       <c r="C494" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D494" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E494" t="b">
         <v>0</v>
@@ -24440,10 +24440,10 @@
         <v>527</v>
       </c>
       <c r="C495" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D495" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E495" t="b">
         <v>0</v>
@@ -24484,10 +24484,10 @@
         <v>528</v>
       </c>
       <c r="C496" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D496" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E496" t="b">
         <v>0</v>
@@ -24528,10 +24528,10 @@
         <v>529</v>
       </c>
       <c r="C497" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D497" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E497" t="b">
         <v>0</v>
@@ -24572,10 +24572,10 @@
         <v>530</v>
       </c>
       <c r="C498" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D498" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E498" t="b">
         <v>0</v>
@@ -24616,10 +24616,10 @@
         <v>531</v>
       </c>
       <c r="C499" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D499" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E499" t="b">
         <v>0</v>
@@ -24660,10 +24660,10 @@
         <v>532</v>
       </c>
       <c r="C500" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D500" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E500" t="b">
         <v>0</v>
@@ -24704,10 +24704,10 @@
         <v>533</v>
       </c>
       <c r="C501" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D501" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E501" t="b">
         <v>0</v>
@@ -24748,10 +24748,10 @@
         <v>534</v>
       </c>
       <c r="C502" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D502" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E502" t="b">
         <v>0</v>
@@ -24792,10 +24792,10 @@
         <v>535</v>
       </c>
       <c r="C503" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D503" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E503" t="b">
         <v>0</v>
@@ -24836,10 +24836,10 @@
         <v>536</v>
       </c>
       <c r="C504" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D504" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E504" t="b">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>537</v>
       </c>
       <c r="C505" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D505" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E505" t="b">
         <v>0</v>
@@ -24924,10 +24924,10 @@
         <v>538</v>
       </c>
       <c r="C506" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D506" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E506" t="b">
         <v>0</v>
@@ -24968,10 +24968,10 @@
         <v>539</v>
       </c>
       <c r="C507" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D507" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E507" t="b">
         <v>0</v>
@@ -25012,10 +25012,10 @@
         <v>540</v>
       </c>
       <c r="C508" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D508" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E508" t="b">
         <v>0</v>
@@ -25056,10 +25056,10 @@
         <v>541</v>
       </c>
       <c r="C509" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D509" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E509" t="b">
         <v>0</v>
@@ -25100,10 +25100,10 @@
         <v>542</v>
       </c>
       <c r="C510" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D510" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E510" t="b">
         <v>1</v>
@@ -25144,10 +25144,10 @@
         <v>543</v>
       </c>
       <c r="C511" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D511" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E511" t="b">
         <v>0</v>
@@ -25188,10 +25188,10 @@
         <v>544</v>
       </c>
       <c r="C512" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D512" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E512" t="b">
         <v>0</v>
@@ -25232,10 +25232,10 @@
         <v>545</v>
       </c>
       <c r="C513" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D513" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E513" t="b">
         <v>0</v>
@@ -25276,10 +25276,10 @@
         <v>546</v>
       </c>
       <c r="C514" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D514" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E514" t="b">
         <v>0</v>
@@ -25320,10 +25320,10 @@
         <v>547</v>
       </c>
       <c r="C515" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D515" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E515" t="b">
         <v>0</v>
@@ -25364,10 +25364,10 @@
         <v>548</v>
       </c>
       <c r="C516" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D516" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E516" t="b">
         <v>0</v>
@@ -25408,10 +25408,10 @@
         <v>549</v>
       </c>
       <c r="C517" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D517" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E517" t="b">
         <v>0</v>
@@ -25452,10 +25452,10 @@
         <v>550</v>
       </c>
       <c r="C518" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D518" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E518" t="b">
         <v>0</v>
@@ -25496,10 +25496,10 @@
         <v>551</v>
       </c>
       <c r="C519" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D519" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E519" t="b">
         <v>0</v>
@@ -25540,10 +25540,10 @@
         <v>552</v>
       </c>
       <c r="C520" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D520" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E520" t="b">
         <v>0</v>
@@ -25584,10 +25584,10 @@
         <v>553</v>
       </c>
       <c r="C521" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D521" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E521" t="b">
         <v>0</v>
@@ -25628,10 +25628,10 @@
         <v>554</v>
       </c>
       <c r="C522" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D522" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E522" t="b">
         <v>0</v>
@@ -25672,10 +25672,10 @@
         <v>555</v>
       </c>
       <c r="C523" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D523" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E523" t="b">
         <v>0</v>
@@ -25716,10 +25716,10 @@
         <v>556</v>
       </c>
       <c r="C524" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D524" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E524" t="b">
         <v>0</v>
@@ -25760,10 +25760,10 @@
         <v>557</v>
       </c>
       <c r="C525" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D525" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E525" t="b">
         <v>0</v>
@@ -25804,10 +25804,10 @@
         <v>558</v>
       </c>
       <c r="C526" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D526" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E526" t="b">
         <v>0</v>
@@ -25848,10 +25848,10 @@
         <v>559</v>
       </c>
       <c r="C527" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D527" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E527" t="b">
         <v>0</v>
@@ -25892,10 +25892,10 @@
         <v>560</v>
       </c>
       <c r="C528" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D528" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E528" t="b">
         <v>1</v>
@@ -25936,10 +25936,10 @@
         <v>561</v>
       </c>
       <c r="C529" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D529" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E529" t="b">
         <v>0</v>
@@ -25980,10 +25980,10 @@
         <v>562</v>
       </c>
       <c r="C530" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D530" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E530" t="b">
         <v>0</v>
@@ -26024,10 +26024,10 @@
         <v>563</v>
       </c>
       <c r="C531" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D531" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E531" t="b">
         <v>0</v>
@@ -26068,10 +26068,10 @@
         <v>564</v>
       </c>
       <c r="C532" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D532" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E532" t="b">
         <v>0</v>
@@ -26112,10 +26112,10 @@
         <v>565</v>
       </c>
       <c r="C533" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D533" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E533" t="b">
         <v>0</v>
@@ -26156,10 +26156,10 @@
         <v>566</v>
       </c>
       <c r="C534" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D534" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E534" t="b">
         <v>0</v>
@@ -26200,10 +26200,10 @@
         <v>567</v>
       </c>
       <c r="C535" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D535" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E535" t="b">
         <v>0</v>
@@ -26244,10 +26244,10 @@
         <v>568</v>
       </c>
       <c r="C536" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D536" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E536" t="b">
         <v>0</v>
@@ -26288,10 +26288,10 @@
         <v>569</v>
       </c>
       <c r="C537" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D537" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E537" t="b">
         <v>0</v>
@@ -26332,10 +26332,10 @@
         <v>570</v>
       </c>
       <c r="C538" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D538" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E538" t="b">
         <v>0</v>
@@ -26376,10 +26376,10 @@
         <v>571</v>
       </c>
       <c r="C539" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D539" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E539" t="b">
         <v>0</v>
@@ -26420,10 +26420,10 @@
         <v>572</v>
       </c>
       <c r="C540" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D540" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E540" t="b">
         <v>0</v>
@@ -26464,10 +26464,10 @@
         <v>573</v>
       </c>
       <c r="C541" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D541" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E541" t="b">
         <v>0</v>
@@ -26508,10 +26508,10 @@
         <v>574</v>
       </c>
       <c r="C542" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D542" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E542" t="b">
         <v>0</v>
@@ -26552,10 +26552,10 @@
         <v>575</v>
       </c>
       <c r="C543" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D543" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E543" t="b">
         <v>0</v>
@@ -26596,10 +26596,10 @@
         <v>576</v>
       </c>
       <c r="C544" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D544" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E544" t="b">
         <v>0</v>
@@ -26640,10 +26640,10 @@
         <v>577</v>
       </c>
       <c r="C545" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D545" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E545" t="b">
         <v>0</v>
@@ -26684,10 +26684,10 @@
         <v>578</v>
       </c>
       <c r="C546" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D546" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E546" t="b">
         <v>0</v>
@@ -26728,10 +26728,10 @@
         <v>579</v>
       </c>
       <c r="C547" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D547" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E547" t="b">
         <v>0</v>
@@ -26772,10 +26772,10 @@
         <v>580</v>
       </c>
       <c r="C548" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D548" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E548" t="b">
         <v>0</v>
@@ -26816,10 +26816,10 @@
         <v>581</v>
       </c>
       <c r="C549" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D549" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E549" t="b">
         <v>0</v>
@@ -26860,10 +26860,10 @@
         <v>582</v>
       </c>
       <c r="C550" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D550" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E550" t="b">
         <v>0</v>
@@ -26904,10 +26904,10 @@
         <v>583</v>
       </c>
       <c r="C551" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D551" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E551" t="b">
         <v>0</v>
@@ -26948,10 +26948,10 @@
         <v>584</v>
       </c>
       <c r="C552" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D552" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E552" t="b">
         <v>0</v>
@@ -26992,10 +26992,10 @@
         <v>585</v>
       </c>
       <c r="C553" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D553" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E553" t="b">
         <v>0</v>
@@ -27036,10 +27036,10 @@
         <v>586</v>
       </c>
       <c r="C554" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D554" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E554" t="b">
         <v>0</v>
@@ -27080,10 +27080,10 @@
         <v>587</v>
       </c>
       <c r="C555" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D555" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E555" t="b">
         <v>0</v>
@@ -27124,10 +27124,10 @@
         <v>588</v>
       </c>
       <c r="C556" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D556" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E556" t="b">
         <v>0</v>
@@ -27168,10 +27168,10 @@
         <v>589</v>
       </c>
       <c r="C557" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D557" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E557" t="b">
         <v>0</v>
@@ -27212,10 +27212,10 @@
         <v>590</v>
       </c>
       <c r="C558" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D558" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E558" t="b">
         <v>1</v>
@@ -27256,10 +27256,10 @@
         <v>591</v>
       </c>
       <c r="C559" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D559" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E559" t="b">
         <v>0</v>
@@ -27300,10 +27300,10 @@
         <v>592</v>
       </c>
       <c r="C560" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D560" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E560" t="b">
         <v>1</v>
@@ -27344,10 +27344,10 @@
         <v>593</v>
       </c>
       <c r="C561" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D561" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E561" t="b">
         <v>0</v>
@@ -27388,10 +27388,10 @@
         <v>594</v>
       </c>
       <c r="C562" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D562" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E562" t="b">
         <v>0</v>
@@ -27432,10 +27432,10 @@
         <v>595</v>
       </c>
       <c r="C563" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D563" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E563" t="b">
         <v>0</v>
@@ -27476,10 +27476,10 @@
         <v>596</v>
       </c>
       <c r="C564" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D564" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E564" t="b">
         <v>0</v>
@@ -27520,10 +27520,10 @@
         <v>597</v>
       </c>
       <c r="C565" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D565" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E565" t="b">
         <v>0</v>
@@ -27564,10 +27564,10 @@
         <v>598</v>
       </c>
       <c r="C566" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D566" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E566" t="b">
         <v>0</v>
@@ -27608,10 +27608,10 @@
         <v>599</v>
       </c>
       <c r="C567" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D567" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E567" t="b">
         <v>0</v>
@@ -27652,10 +27652,10 @@
         <v>600</v>
       </c>
       <c r="C568" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D568" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E568" t="b">
         <v>0</v>
@@ -27696,10 +27696,10 @@
         <v>601</v>
       </c>
       <c r="C569" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D569" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E569" t="b">
         <v>1</v>
@@ -27740,10 +27740,10 @@
         <v>602</v>
       </c>
       <c r="C570" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D570" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E570" t="b">
         <v>0</v>
@@ -27784,10 +27784,10 @@
         <v>603</v>
       </c>
       <c r="C571" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D571" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E571" t="b">
         <v>0</v>
@@ -27828,10 +27828,10 @@
         <v>604</v>
       </c>
       <c r="C572" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D572" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E572" t="b">
         <v>0</v>
@@ -27872,10 +27872,10 @@
         <v>605</v>
       </c>
       <c r="C573" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D573" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E573" t="b">
         <v>1</v>
@@ -27916,10 +27916,10 @@
         <v>606</v>
       </c>
       <c r="C574" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D574" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E574" t="b">
         <v>0</v>
@@ -27960,10 +27960,10 @@
         <v>607</v>
       </c>
       <c r="C575" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D575" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E575" t="b">
         <v>0</v>
@@ -28004,10 +28004,10 @@
         <v>608</v>
       </c>
       <c r="C576" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D576" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E576" t="b">
         <v>0</v>
@@ -28048,10 +28048,10 @@
         <v>609</v>
       </c>
       <c r="C577" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D577" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E577" t="b">
         <v>0</v>
@@ -28092,10 +28092,10 @@
         <v>610</v>
       </c>
       <c r="C578" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D578" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E578" t="b">
         <v>0</v>
@@ -28136,10 +28136,10 @@
         <v>611</v>
       </c>
       <c r="C579" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D579" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E579" t="b">
         <v>0</v>
@@ -28180,10 +28180,10 @@
         <v>612</v>
       </c>
       <c r="C580" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D580" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E580" t="b">
         <v>1</v>
@@ -28224,10 +28224,10 @@
         <v>613</v>
       </c>
       <c r="C581" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D581" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E581" t="b">
         <v>0</v>
@@ -28268,10 +28268,10 @@
         <v>614</v>
       </c>
       <c r="C582" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D582" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E582" t="b">
         <v>0</v>
@@ -28312,10 +28312,10 @@
         <v>615</v>
       </c>
       <c r="C583" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D583" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E583" t="b">
         <v>0</v>
@@ -28356,10 +28356,10 @@
         <v>616</v>
       </c>
       <c r="C584" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D584" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E584" t="b">
         <v>0</v>
@@ -28400,10 +28400,10 @@
         <v>617</v>
       </c>
       <c r="C585" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D585" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E585" t="b">
         <v>0</v>
@@ -28444,10 +28444,10 @@
         <v>618</v>
       </c>
       <c r="C586" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D586" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E586" t="b">
         <v>0</v>
@@ -28488,10 +28488,10 @@
         <v>619</v>
       </c>
       <c r="C587" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D587" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E587" t="b">
         <v>0</v>
@@ -28532,10 +28532,10 @@
         <v>620</v>
       </c>
       <c r="C588" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D588" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E588" t="b">
         <v>0</v>
@@ -28576,10 +28576,10 @@
         <v>621</v>
       </c>
       <c r="C589" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D589" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E589" t="b">
         <v>0</v>
@@ -28620,10 +28620,10 @@
         <v>622</v>
       </c>
       <c r="C590" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D590" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E590" t="b">
         <v>0</v>
@@ -28664,10 +28664,10 @@
         <v>623</v>
       </c>
       <c r="C591" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D591" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E591" t="b">
         <v>0</v>
@@ -28708,10 +28708,10 @@
         <v>624</v>
       </c>
       <c r="C592" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D592" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E592" t="b">
         <v>0</v>
@@ -28752,10 +28752,10 @@
         <v>625</v>
       </c>
       <c r="C593" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D593" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E593" t="b">
         <v>0</v>
@@ -28796,10 +28796,10 @@
         <v>626</v>
       </c>
       <c r="C594" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D594" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E594" t="b">
         <v>0</v>
@@ -28840,10 +28840,10 @@
         <v>627</v>
       </c>
       <c r="C595" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D595" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E595" t="b">
         <v>0</v>
@@ -28884,10 +28884,10 @@
         <v>628</v>
       </c>
       <c r="C596" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D596" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E596" t="b">
         <v>0</v>
@@ -28928,10 +28928,10 @@
         <v>629</v>
       </c>
       <c r="C597" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D597" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E597" t="b">
         <v>0</v>
@@ -28972,10 +28972,10 @@
         <v>630</v>
       </c>
       <c r="C598" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D598" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E598" t="b">
         <v>1</v>
@@ -29016,10 +29016,10 @@
         <v>631</v>
       </c>
       <c r="C599" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D599" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E599" t="b">
         <v>0</v>
@@ -29060,10 +29060,10 @@
         <v>632</v>
       </c>
       <c r="C600" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D600" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E600" t="b">
         <v>0</v>
@@ -29104,10 +29104,10 @@
         <v>633</v>
       </c>
       <c r="C601" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D601" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E601" t="b">
         <v>0</v>
@@ -29148,10 +29148,10 @@
         <v>634</v>
       </c>
       <c r="C602" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D602" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E602" t="b">
         <v>0</v>
@@ -29192,10 +29192,10 @@
         <v>635</v>
       </c>
       <c r="C603" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D603" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E603" t="b">
         <v>0</v>
@@ -29236,10 +29236,10 @@
         <v>636</v>
       </c>
       <c r="C604" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D604" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E604" t="b">
         <v>0</v>
@@ -29280,10 +29280,10 @@
         <v>637</v>
       </c>
       <c r="C605" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D605" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E605" t="b">
         <v>0</v>
@@ -29324,10 +29324,10 @@
         <v>638</v>
       </c>
       <c r="C606" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D606" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E606" t="b">
         <v>0</v>
@@ -29368,10 +29368,10 @@
         <v>639</v>
       </c>
       <c r="C607" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D607" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E607" t="b">
         <v>0</v>
@@ -29412,10 +29412,10 @@
         <v>640</v>
       </c>
       <c r="C608" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D608" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E608" t="b">
         <v>0</v>
@@ -29456,10 +29456,10 @@
         <v>641</v>
       </c>
       <c r="C609" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D609" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E609" t="b">
         <v>0</v>
@@ -29500,10 +29500,10 @@
         <v>642</v>
       </c>
       <c r="C610" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D610" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E610" t="b">
         <v>0</v>
@@ -29544,10 +29544,10 @@
         <v>643</v>
       </c>
       <c r="C611" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D611" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E611" t="b">
         <v>0</v>
@@ -29588,10 +29588,10 @@
         <v>644</v>
       </c>
       <c r="C612" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D612" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E612" t="b">
         <v>0</v>
@@ -29632,10 +29632,10 @@
         <v>645</v>
       </c>
       <c r="C613" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D613" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E613" t="b">
         <v>0</v>
@@ -29676,10 +29676,10 @@
         <v>646</v>
       </c>
       <c r="C614" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D614" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E614" t="b">
         <v>0</v>
@@ -29720,10 +29720,10 @@
         <v>647</v>
       </c>
       <c r="C615" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D615" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E615" t="b">
         <v>0</v>
@@ -29764,10 +29764,10 @@
         <v>648</v>
       </c>
       <c r="C616" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D616" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E616" t="b">
         <v>0</v>
@@ -29808,10 +29808,10 @@
         <v>649</v>
       </c>
       <c r="C617" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D617" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E617" t="b">
         <v>0</v>
@@ -29852,10 +29852,10 @@
         <v>650</v>
       </c>
       <c r="C618" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D618" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E618" t="b">
         <v>1</v>
@@ -29896,10 +29896,10 @@
         <v>651</v>
       </c>
       <c r="C619" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D619" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E619" t="b">
         <v>0</v>
@@ -29940,10 +29940,10 @@
         <v>652</v>
       </c>
       <c r="C620" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D620" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E620" t="b">
         <v>0</v>
@@ -29984,10 +29984,10 @@
         <v>653</v>
       </c>
       <c r="C621" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D621" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E621" t="b">
         <v>0</v>
@@ -30028,10 +30028,10 @@
         <v>654</v>
       </c>
       <c r="C622" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D622" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E622" t="b">
         <v>0</v>
@@ -30072,10 +30072,10 @@
         <v>655</v>
       </c>
       <c r="C623" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D623" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E623" t="b">
         <v>0</v>
@@ -30116,10 +30116,10 @@
         <v>656</v>
       </c>
       <c r="C624" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D624" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E624" t="b">
         <v>0</v>
@@ -30160,10 +30160,10 @@
         <v>657</v>
       </c>
       <c r="C625" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D625" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E625" t="b">
         <v>0</v>
@@ -30204,10 +30204,10 @@
         <v>658</v>
       </c>
       <c r="C626" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D626" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E626" t="b">
         <v>0</v>
@@ -30248,10 +30248,10 @@
         <v>659</v>
       </c>
       <c r="C627" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D627" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E627" t="b">
         <v>0</v>
@@ -30292,10 +30292,10 @@
         <v>660</v>
       </c>
       <c r="C628" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D628" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E628" t="b">
         <v>0</v>
@@ -30336,10 +30336,10 @@
         <v>661</v>
       </c>
       <c r="C629" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D629" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E629" t="b">
         <v>0</v>
@@ -30380,10 +30380,10 @@
         <v>662</v>
       </c>
       <c r="C630" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D630" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E630" t="b">
         <v>0</v>
@@ -30424,10 +30424,10 @@
         <v>663</v>
       </c>
       <c r="C631" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D631" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E631" t="b">
         <v>0</v>
@@ -30468,10 +30468,10 @@
         <v>664</v>
       </c>
       <c r="C632" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D632" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E632" t="b">
         <v>0</v>
@@ -30512,10 +30512,10 @@
         <v>665</v>
       </c>
       <c r="C633" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D633" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E633" t="b">
         <v>0</v>
@@ -30556,10 +30556,10 @@
         <v>666</v>
       </c>
       <c r="C634" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D634" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E634" t="b">
         <v>0</v>
@@ -30600,10 +30600,10 @@
         <v>667</v>
       </c>
       <c r="C635" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D635" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E635" t="b">
         <v>0</v>
@@ -30644,10 +30644,10 @@
         <v>668</v>
       </c>
       <c r="C636" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D636" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E636" t="b">
         <v>0</v>
@@ -30688,10 +30688,10 @@
         <v>669</v>
       </c>
       <c r="C637" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D637" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E637" t="b">
         <v>0</v>
@@ -30732,10 +30732,10 @@
         <v>670</v>
       </c>
       <c r="C638" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D638" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E638" t="b">
         <v>0</v>
@@ -30776,10 +30776,10 @@
         <v>671</v>
       </c>
       <c r="C639" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D639" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E639" t="b">
         <v>0</v>
@@ -30820,10 +30820,10 @@
         <v>672</v>
       </c>
       <c r="C640" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D640" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E640" t="b">
         <v>0</v>
@@ -30864,10 +30864,10 @@
         <v>673</v>
       </c>
       <c r="C641" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D641" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E641" t="b">
         <v>0</v>
@@ -30908,10 +30908,10 @@
         <v>674</v>
       </c>
       <c r="C642" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D642" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E642" t="b">
         <v>0</v>
@@ -30952,10 +30952,10 @@
         <v>675</v>
       </c>
       <c r="C643" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D643" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E643" t="b">
         <v>0</v>
@@ -30996,10 +30996,10 @@
         <v>676</v>
       </c>
       <c r="C644" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D644" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E644" t="b">
         <v>0</v>
@@ -31040,10 +31040,10 @@
         <v>677</v>
       </c>
       <c r="C645" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D645" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E645" t="b">
         <v>0</v>
@@ -31141,10 +31141,10 @@
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -31188,10 +31188,10 @@
         <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -31235,10 +31235,10 @@
         <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -31282,10 +31282,10 @@
         <v>220</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -31329,10 +31329,10 @@
         <v>256</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -31376,10 +31376,10 @@
         <v>262</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -31423,10 +31423,10 @@
         <v>268</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -31470,10 +31470,10 @@
         <v>321</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -31517,10 +31517,10 @@
         <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -31564,10 +31564,10 @@
         <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -31611,10 +31611,10 @@
         <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -31658,10 +31658,10 @@
         <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -31705,10 +31705,10 @@
         <v>199</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -31752,10 +31752,10 @@
         <v>346</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -31799,10 +31799,10 @@
         <v>417</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -31846,10 +31846,10 @@
         <v>471</v>
       </c>
       <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
         <v>17</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -31950,10 +31950,10 @@
         <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -31997,10 +31997,10 @@
         <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -32044,10 +32044,10 @@
         <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -32091,10 +32091,10 @@
         <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -32138,10 +32138,10 @@
         <v>179</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -32185,10 +32185,10 @@
         <v>198</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -32232,10 +32232,10 @@
         <v>204</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -32279,10 +32279,10 @@
         <v>229</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -32326,10 +32326,10 @@
         <v>233</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -32373,10 +32373,10 @@
         <v>258</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -32420,10 +32420,10 @@
         <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -32467,10 +32467,10 @@
         <v>293</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -32514,10 +32514,10 @@
         <v>297</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -32561,10 +32561,10 @@
         <v>301</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -32608,10 +32608,10 @@
         <v>308</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -32655,10 +32655,10 @@
         <v>316</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -32702,10 +32702,10 @@
         <v>326</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -32749,10 +32749,10 @@
         <v>345</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -32796,10 +32796,10 @@
         <v>351</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -32843,10 +32843,10 @@
         <v>360</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -32890,10 +32890,10 @@
         <v>478</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -32937,10 +32937,10 @@
         <v>493</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -32984,10 +32984,10 @@
         <v>497</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -33031,10 +33031,10 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -33078,10 +33078,10 @@
         <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -33125,10 +33125,10 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -33172,10 +33172,10 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -33219,10 +33219,10 @@
         <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -33266,10 +33266,10 @@
         <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -33313,10 +33313,10 @@
         <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -33360,10 +33360,10 @@
         <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -33407,10 +33407,10 @@
         <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -33454,10 +33454,10 @@
         <v>174</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -33501,10 +33501,10 @@
         <v>188</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>244</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -33595,10 +33595,10 @@
         <v>282</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -33642,10 +33642,10 @@
         <v>290</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -33689,10 +33689,10 @@
         <v>305</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -33736,10 +33736,10 @@
         <v>319</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -33783,10 +33783,10 @@
         <v>335</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -33830,10 +33830,10 @@
         <v>341</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -33877,10 +33877,10 @@
         <v>399</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -33924,10 +33924,10 @@
         <v>453</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -33971,10 +33971,10 @@
         <v>482</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -34018,10 +34018,10 @@
         <v>528</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -34065,10 +34065,10 @@
         <v>677</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
